--- a/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tareas del hogar realizadas por el/la entrevistado/a</t>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,1; 50,21</t>
+          <t>28,48; 49,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,19; 64,14</t>
+          <t>43,12; 65,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,64; 49,58</t>
+          <t>26,05; 50,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,82; 84,99</t>
+          <t>47,38; 84,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,39; 59,87</t>
+          <t>37,17; 59,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,56; 58,15</t>
+          <t>38,01; 59,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,34; 43,25</t>
+          <t>23,48; 45,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,76; 82,43</t>
+          <t>61,98; 82,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,69; 52,17</t>
+          <t>36,09; 51,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,9; 58,3</t>
+          <t>44,05; 58,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,36; 43,46</t>
+          <t>26,78; 42,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,08; 80,42</t>
+          <t>58,78; 80,49</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,75; 41,9</t>
+          <t>33,37; 42,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,16; 39,14</t>
+          <t>30,5; 39,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,11; 39,63</t>
+          <t>31,57; 40,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,43; 89,7</t>
+          <t>83,73; 89,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,3; 42,59</t>
+          <t>34,56; 43,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,3; 37,78</t>
+          <t>29,19; 37,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,96</t>
+          <t>30,71; 38,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,41; 88,86</t>
+          <t>83,22; 89,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,04; 41,02</t>
+          <t>34,9; 40,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,06; 37,44</t>
+          <t>31,51; 37,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,39; 38,14</t>
+          <t>32,05; 37,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,36; 88,78</t>
+          <t>84,44; 88,84</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,48; 35,93</t>
+          <t>23,05; 35,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,49; 30,67</t>
+          <t>17,92; 31,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,67; 30,27</t>
+          <t>18,6; 30,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,49; 92,72</t>
+          <t>84,69; 93,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 28,04</t>
+          <t>15,47; 28,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,71; 35,0</t>
+          <t>21,25; 34,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,95; 35,35</t>
+          <t>22,94; 35,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,71; 93,58</t>
+          <t>85,46; 93,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,56; 30,4</t>
+          <t>21,76; 30,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,06</t>
+          <t>21,88; 31,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,01; 30,54</t>
+          <t>22,16; 30,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86,43; 92,31</t>
+          <t>86,39; 92,37</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,87; 38,82</t>
+          <t>31,95; 38,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 37,98</t>
+          <t>30,61; 37,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,1; 35,95</t>
+          <t>29,07; 35,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,84; 88,71</t>
+          <t>82,71; 88,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,55; 39,17</t>
+          <t>32,64; 39,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,21</t>
+          <t>30,38; 37,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,84; 36,52</t>
+          <t>30,09; 36,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,58; 88,14</t>
+          <t>83,7; 88,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,33; 37,99</t>
+          <t>33,34; 38,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,71; 36,52</t>
+          <t>31,76; 36,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,41; 35,26</t>
+          <t>30,42; 35,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,03; 87,73</t>
+          <t>83,91; 87,88</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>21828</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29872</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14846</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38631</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25124</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30270</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16714</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>45489</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>46952</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>60143</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31560</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>84121</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>16081; 27733</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23922; 36365</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10586; 20409</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25905; 46040</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>19093; 30777</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23597; 36666</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12031; 23159</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>38428; 51205</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>38920; 56054</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>51796; 69196</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24608; 39293</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>68587; 93917</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>116138</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106228</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>123792</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>399607</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>136638</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>113715</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>131810</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>445828</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>252776</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>219943</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>255602</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>845435</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>103567; 130641</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92926; 121053</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110106; 139512</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>385603; 413909</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>122207; 152825</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>99181; 128826</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>116667; 147483</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>429923; 459924</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>231689; 270879</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>203036; 242401</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>233485; 276436</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>825124; 868038</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>40073</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27834</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32346</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133328</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26921</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37880</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40408</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>165297</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>66994</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65714</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>72755</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>298625</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>31481; 48522</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20938; 36658</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25304; 41570</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>126652; 139162</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19107; 34818</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>29094; 47730</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32107; 49361</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>156689; 171479</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>56612; 79666</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>55522; 78908</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>61158; 85452</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>287581; 307488</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>178038</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163934</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>170985</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>571565</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>656615</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>366721</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>345800</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>359917</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1228181</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>160825; 194731</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>146023; 180617</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>152738; 189092</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>549818; 589738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>172522; 206363</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>163677; 200904</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>171826; 209631</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>637741; 674181</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>344083; 397200</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>322566; 370197</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>333531; 387098</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1197153; 1253761</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,48; 49,12</t>
+          <t>29,34; 49,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,12; 65,54</t>
+          <t>43,32; 65,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,05; 50,22</t>
+          <t>25,16; 49,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,38; 84,2</t>
+          <t>47,85; 84,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,17; 59,91</t>
+          <t>38,56; 59,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,01; 59,05</t>
+          <t>38,97; 59,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,48; 45,2</t>
+          <t>22,48; 42,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,98; 82,58</t>
+          <t>61,93; 82,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,09; 51,98</t>
+          <t>36,25; 51,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,05; 58,85</t>
+          <t>42,94; 58,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,78; 42,77</t>
+          <t>25,97; 42,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,78; 80,49</t>
+          <t>60,56; 80,29</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,37; 42,1</t>
+          <t>33,16; 42,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,5; 39,73</t>
+          <t>30,69; 39,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,57; 40,01</t>
+          <t>31,16; 39,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,73; 89,88</t>
+          <t>83,46; 89,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,56; 43,22</t>
+          <t>34,39; 43,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 37,91</t>
+          <t>29,3; 37,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,71; 38,83</t>
+          <t>30,64; 38,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,22; 89,03</t>
+          <t>83,41; 89,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,9; 40,8</t>
+          <t>35,44; 41,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,51; 37,61</t>
+          <t>31,18; 37,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,05; 37,94</t>
+          <t>32,08; 37,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,44; 88,84</t>
+          <t>84,52; 88,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,05; 35,53</t>
+          <t>23,24; 36,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,92; 31,38</t>
+          <t>17,82; 30,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 30,56</t>
+          <t>18,38; 30,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,69; 93,05</t>
+          <t>84,41; 92,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 28,18</t>
+          <t>16,44; 28,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 34,87</t>
+          <t>22,15; 35,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,94; 35,28</t>
+          <t>23,11; 36,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,46; 93,53</t>
+          <t>85,57; 93,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,76; 30,63</t>
+          <t>20,89; 30,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,88; 31,1</t>
+          <t>21,66; 30,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,16; 30,97</t>
+          <t>22,17; 30,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86,39; 92,37</t>
+          <t>86,27; 92,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,95; 38,69</t>
+          <t>32,07; 38,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,61; 37,87</t>
+          <t>31,15; 38,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,07; 35,99</t>
+          <t>29,41; 36,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,71; 88,72</t>
+          <t>82,6; 88,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,64; 39,04</t>
+          <t>32,32; 39,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,29</t>
+          <t>30,72; 37,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,09; 36,71</t>
+          <t>29,98; 36,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,7; 88,48</t>
+          <t>83,6; 88,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,34; 38,49</t>
+          <t>33,31; 37,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,76; 36,45</t>
+          <t>31,8; 36,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 35,31</t>
+          <t>30,49; 34,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,91; 87,88</t>
+          <t>84,32; 87,81</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16081; 27733</t>
+          <t>16568; 27703</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23922; 36365</t>
+          <t>24034; 36159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10586; 20409</t>
+          <t>10224; 20019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25905; 46040</t>
+          <t>26162; 46302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19093; 30777</t>
+          <t>19807; 30529</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23597; 36666</t>
+          <t>24199; 36851</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12031; 23159</t>
+          <t>11520; 21791</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38428; 51205</t>
+          <t>38397; 51280</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38920; 56054</t>
+          <t>39093; 55699</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51796; 69196</t>
+          <t>50484; 68471</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24608; 39293</t>
+          <t>23857; 39477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68587; 93917</t>
+          <t>70657; 93690</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>103567; 130641</t>
+          <t>102910; 130710</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92926; 121053</t>
+          <t>93502; 121146</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110106; 139512</t>
+          <t>108647; 139270</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>385603; 413909</t>
+          <t>384341; 413815</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>122207; 152825</t>
+          <t>121606; 152311</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99181; 128826</t>
+          <t>99557; 127512</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>116667; 147483</t>
+          <t>116404; 147849</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>429923; 459924</t>
+          <t>430897; 461211</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>231689; 270879</t>
+          <t>235330; 273841</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203036; 242401</t>
+          <t>200919; 239763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>233485; 276436</t>
+          <t>233704; 274681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>825124; 868038</t>
+          <t>825876; 867435</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31481; 48522</t>
+          <t>31739; 49600</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20938; 36658</t>
+          <t>20823; 35997</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25304; 41570</t>
+          <t>24997; 41654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126652; 139162</t>
+          <t>126229; 139012</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19107; 34818</t>
+          <t>20311; 34635</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29094; 47730</t>
+          <t>30319; 48303</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32107; 49361</t>
+          <t>32332; 50578</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>156689; 171479</t>
+          <t>156896; 171638</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56612; 79666</t>
+          <t>54350; 78185</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55522; 78908</t>
+          <t>54954; 76907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61158; 85452</t>
+          <t>61172; 85510</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>287581; 307488</t>
+          <t>287204; 306712</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>160825; 194731</t>
+          <t>161434; 195904</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>146023; 180617</t>
+          <t>148578; 181319</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>152738; 189092</t>
+          <t>154519; 189234</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>549818; 589738</t>
+          <t>549081; 588310</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>172522; 206363</t>
+          <t>170832; 207188</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>163677; 200904</t>
+          <t>165504; 202389</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>171826; 209631</t>
+          <t>171223; 207722</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>637741; 674181</t>
+          <t>637030; 673605</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>344083; 397200</t>
+          <t>343708; 389694</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>322566; 370197</t>
+          <t>323044; 373546</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>333531; 387098</t>
+          <t>334332; 382916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1197153; 1253761</t>
+          <t>1202937; 1252753</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48,91%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>48,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>38,66%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>53,84%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>36,53%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,34; 49,06</t>
+          <t>37,39; 59,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,32; 65,17</t>
+          <t>38,56; 58,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,16; 49,26</t>
+          <t>22,34; 43,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,85; 84,68</t>
+          <t>62,23; 82,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,56; 59,43</t>
+          <t>29,1; 50,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,97; 59,35</t>
+          <t>41,19; 64,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,48; 42,53</t>
+          <t>25,64; 49,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,93; 82,7</t>
+          <t>68,06; 88,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,25; 51,65</t>
+          <t>36,69; 52,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,94; 58,24</t>
+          <t>43,9; 58,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,97; 42,97</t>
+          <t>26,36; 43,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,56; 80,29</t>
+          <t>68,58; 83,53</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>37,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>34,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>35,5%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,16; 42,12</t>
+          <t>34,3; 42,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,69; 39,77</t>
+          <t>29,3; 37,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,16; 39,94</t>
+          <t>30,72; 38,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,46; 89,86</t>
+          <t>82,96; 88,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,39; 43,07</t>
+          <t>32,75; 41,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,3; 37,53</t>
+          <t>30,16; 39,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,64; 38,92</t>
+          <t>31,11; 39,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,41; 89,27</t>
+          <t>83,35; 88,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,44; 41,24</t>
+          <t>35,04; 41,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,18; 37,2</t>
+          <t>31,06; 37,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,08; 37,7</t>
+          <t>32,39; 38,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,52; 88,77</t>
+          <t>83,94; 88,07</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27,67%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28,88%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29,34%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23,78%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89,15%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,24; 36,32</t>
+          <t>16,03; 28,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,82; 30,81</t>
+          <t>21,71; 35,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 30,62</t>
+          <t>22,95; 35,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,41; 92,95</t>
+          <t>85,3; 93,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,44; 28,04</t>
+          <t>23,48; 35,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,15; 35,28</t>
+          <t>17,49; 30,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 36,15</t>
+          <t>18,67; 30,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,57; 93,61</t>
+          <t>84,49; 92,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,89; 30,06</t>
+          <t>21,56; 30,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,66; 30,31</t>
+          <t>21,66; 31,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,17; 30,99</t>
+          <t>22,01; 30,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86,27; 92,13</t>
+          <t>86,32; 92,25</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>32,54%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,07; 38,92</t>
+          <t>32,55; 39,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,02</t>
+          <t>30,1; 37,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 36,02</t>
+          <t>29,84; 36,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82,6; 88,5</t>
+          <t>83,24; 87,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,32; 39,2</t>
+          <t>31,87; 38,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,72; 37,56</t>
+          <t>30,84; 37,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,98; 36,38</t>
+          <t>29,1; 35,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,4</t>
+          <t>84,19; 88,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,31; 37,76</t>
+          <t>33,33; 37,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31,8; 36,78</t>
+          <t>31,71; 36,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,49; 34,92</t>
+          <t>30,41; 35,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,32; 87,81</t>
+          <t>84,65; 87,87</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25124</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30270</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16714</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41893</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>21828</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>29872</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>14846</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38631</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25124</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30270</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16714</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45489</t>
+          <t>37613</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84121</t>
+          <t>79507</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16568; 27703</t>
+          <t>19206; 30755</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24034; 36159</t>
+          <t>23945; 36105</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10224; 20019</t>
+          <t>11448; 22159</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26162; 46302</t>
+          <t>35307; 46822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19807; 30529</t>
+          <t>16432; 28349</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24199; 36851</t>
+          <t>22852; 35588</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11520; 21791</t>
+          <t>10420; 20152</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38397; 51280</t>
+          <t>31824; 41272</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39093; 55699</t>
+          <t>39564; 56258</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50484; 68471</t>
+          <t>51613; 68544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23857; 39477</t>
+          <t>24215; 39930</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70657; 93690</t>
+          <t>70974; 86443</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>554</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>136638</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>113715</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>131810</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>408110</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>116138</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>106228</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>123792</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>399607</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>136638</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>113715</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>131810</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>445828</t>
+          <t>373396</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>845435</t>
+          <t>781506</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>102910; 130710</t>
+          <t>121287; 150630</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93502; 121146</t>
+          <t>99569; 128386</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108647; 139270</t>
+          <t>116678; 147988</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>384341; 413815</t>
+          <t>394619; 421508</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121606; 152311</t>
+          <t>101622; 130011</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99557; 127512</t>
+          <t>91889; 119232</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>116404; 147849</t>
+          <t>108489; 138190</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>430897; 461211</t>
+          <t>360453; 384853</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>235330; 273841</t>
+          <t>232650; 272348</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200919; 239763</t>
+          <t>200164; 241304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>233704; 274681</t>
+          <t>235955; 277891</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>825876; 867435</t>
+          <t>762266; 799746</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>206</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26921</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37880</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40408</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151863</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>40073</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>27834</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>32346</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>133328</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26921</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37880</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40408</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>165297</t>
+          <t>133941</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>298625</t>
+          <t>285803</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31739; 49600</t>
+          <t>19803; 34644</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20823; 35997</t>
+          <t>29719; 47917</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24997; 41654</t>
+          <t>32113; 49462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126229; 139012</t>
+          <t>143653; 157590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20311; 34635</t>
+          <t>32070; 49068</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30319; 48303</t>
+          <t>20438; 35834</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32332; 50578</t>
+          <t>25391; 41180</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>156896; 171638</t>
+          <t>126714; 139349</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54350; 78185</t>
+          <t>56073; 79080</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54954; 76907</t>
+          <t>54969; 78802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61172; 85510</t>
+          <t>60746; 84266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>287204; 306712</t>
+          <t>274830; 293734</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>816</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>571565</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>181865</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>656615</t>
+          <t>544950</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1228181</t>
+          <t>1146815</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>161434; 195904</t>
+          <t>172022; 207056</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148578; 181319</t>
+          <t>162166; 200479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154519; 189234</t>
+          <t>170425; 208535</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>549081; 588310</t>
+          <t>583378; 616585</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>170832; 207188</t>
+          <t>160422; 195426</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>165504; 202389</t>
+          <t>147102; 181161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>171223; 207722</t>
+          <t>152883; 188892</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>637030; 673605</t>
+          <t>529731; 559865</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>343708; 389694</t>
+          <t>343940; 392042</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>323044; 373546</t>
+          <t>322120; 370964</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>334332; 382916</t>
+          <t>333384; 386607</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1202937; 1252753</t>
+          <t>1125822; 1168626</t>
         </is>
       </c>
     </row>
